--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/20.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/20.xlsx
@@ -426,13 +426,13 @@
         <v>-15.08276024125483</v>
       </c>
       <c r="E2">
-        <v>-6.16336841299715</v>
+        <v>-3.663551134334944</v>
       </c>
       <c r="F2">
-        <v>-5.521348046720956</v>
+        <v>-6.142705607193462</v>
       </c>
       <c r="G2">
-        <v>-7.297721389800189</v>
+        <v>-6.344386901401804</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.40172798099707</v>
       </c>
       <c r="E3">
-        <v>-6.410935558522481</v>
+        <v>-4.03388068173421</v>
       </c>
       <c r="F3">
-        <v>-5.678327811388477</v>
+        <v>-5.899737992645743</v>
       </c>
       <c r="G3">
-        <v>-7.298562268367164</v>
+        <v>-6.011160629600924</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.96594129312765</v>
       </c>
       <c r="E4">
-        <v>-6.992115384192887</v>
+        <v>-4.852619725372996</v>
       </c>
       <c r="F4">
-        <v>-5.717473969742572</v>
+        <v>-5.775700742852753</v>
       </c>
       <c r="G4">
-        <v>-7.066291082786358</v>
+        <v>-6.282138713626888</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.50578425645756</v>
       </c>
       <c r="E5">
-        <v>-7.787315419939802</v>
+        <v>-5.569608486533436</v>
       </c>
       <c r="F5">
-        <v>-5.39754853837257</v>
+        <v>-5.654638160403216</v>
       </c>
       <c r="G5">
-        <v>-7.444448078646227</v>
+        <v>-6.186238830445281</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.9711285916119</v>
       </c>
       <c r="E6">
-        <v>-7.755996493702754</v>
+        <v>-6.58495122921523</v>
       </c>
       <c r="F6">
-        <v>-5.311196206835138</v>
+        <v>-5.552497974535829</v>
       </c>
       <c r="G6">
-        <v>-7.442772942603356</v>
+        <v>-6.880619136216334</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-22.22043064586427</v>
       </c>
       <c r="E7">
-        <v>-9.260600096647261</v>
+        <v>-6.756064148069062</v>
       </c>
       <c r="F7">
-        <v>-5.753513750336171</v>
+        <v>-5.65597100355432</v>
       </c>
       <c r="G7">
-        <v>-6.585278747566872</v>
+        <v>-6.311576084562088</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-23.15919093207151</v>
       </c>
       <c r="E8">
-        <v>-10.2986984212176</v>
+        <v>-7.456569263841581</v>
       </c>
       <c r="F8">
-        <v>-5.640234508003338</v>
+        <v>-5.588908863725881</v>
       </c>
       <c r="G8">
-        <v>-8.028590528505088</v>
+        <v>-6.222588620466478</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-23.68145510854058</v>
       </c>
       <c r="E9">
-        <v>-10.11867346551667</v>
+        <v>-8.887689319063622</v>
       </c>
       <c r="F9">
-        <v>-5.643216630653416</v>
+        <v>-5.471410746210591</v>
       </c>
       <c r="G9">
-        <v>-6.255217357301535</v>
+        <v>-5.944026076610044</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-23.7245955884488</v>
       </c>
       <c r="E10">
-        <v>-10.65524782221152</v>
+        <v>-8.453132424813568</v>
       </c>
       <c r="F10">
-        <v>-5.417086411934999</v>
+        <v>-5.550175232338379</v>
       </c>
       <c r="G10">
-        <v>-6.906567192153141</v>
+        <v>-5.539864745539199</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-23.25150854895671</v>
       </c>
       <c r="E11">
-        <v>-11.53065166110829</v>
+        <v>-9.683061436822829</v>
       </c>
       <c r="F11">
-        <v>-4.98938706799117</v>
+        <v>-5.115033007280396</v>
       </c>
       <c r="G11">
-        <v>-6.716710716021478</v>
+        <v>-5.750736564754156</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-22.27140480098532</v>
       </c>
       <c r="E12">
-        <v>-11.63395973864527</v>
+        <v>-9.805180795387674</v>
       </c>
       <c r="F12">
-        <v>-5.002849695021467</v>
+        <v>-5.3651270665944</v>
       </c>
       <c r="G12">
-        <v>-5.777760547991226</v>
+        <v>-5.15743383538813</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-20.82557671897831</v>
       </c>
       <c r="E13">
-        <v>-11.64951957533563</v>
+        <v>-10.12642168454379</v>
       </c>
       <c r="F13">
-        <v>-5.219817341897519</v>
+        <v>-5.133101357070259</v>
       </c>
       <c r="G13">
-        <v>-5.662583358134443</v>
+        <v>-4.804943499094231</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-19.00000563209073</v>
       </c>
       <c r="E14">
-        <v>-13.56940688715354</v>
+        <v>-11.29289771875758</v>
       </c>
       <c r="F14">
-        <v>-4.58190651561487</v>
+        <v>-5.121818993044129</v>
       </c>
       <c r="G14">
-        <v>-6.007807046969642</v>
+        <v>-4.793257273340604</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-16.90570346555503</v>
       </c>
       <c r="E15">
-        <v>-13.46398401225498</v>
+        <v>-11.48058938095349</v>
       </c>
       <c r="F15">
-        <v>-4.606267972563801</v>
+        <v>-4.895144536942072</v>
       </c>
       <c r="G15">
-        <v>-4.811968476728564</v>
+        <v>-4.38600389273608</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.67075329587036</v>
       </c>
       <c r="E16">
-        <v>-14.47727082773729</v>
+        <v>-12.66977571231574</v>
       </c>
       <c r="F16">
-        <v>-4.46619270148521</v>
+        <v>-4.576863414866627</v>
       </c>
       <c r="G16">
-        <v>-4.412945112334669</v>
+        <v>-3.726427352219385</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.42767744232526</v>
       </c>
       <c r="E17">
-        <v>-15.07713060868934</v>
+        <v>-13.23891885407376</v>
       </c>
       <c r="F17">
-        <v>-4.122248757271036</v>
+        <v>-4.528841299791534</v>
       </c>
       <c r="G17">
-        <v>-3.281132492823096</v>
+        <v>-3.041541691054962</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.29980506774116</v>
       </c>
       <c r="E18">
-        <v>-14.50468168090572</v>
+        <v>-14.50317822753517</v>
       </c>
       <c r="F18">
-        <v>-3.767866555414185</v>
+        <v>-3.998639773425294</v>
       </c>
       <c r="G18">
-        <v>-3.687727074865305</v>
+        <v>-2.473561324518822</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.393480685529299</v>
       </c>
       <c r="E19">
-        <v>-16.80035987977615</v>
+        <v>-14.31425029193517</v>
       </c>
       <c r="F19">
-        <v>-3.59564068869814</v>
+        <v>-3.781773187372383</v>
       </c>
       <c r="G19">
-        <v>-3.003556491537365</v>
+        <v>-2.778734033419919</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.795152432522801</v>
       </c>
       <c r="E20">
-        <v>-17.28401901769138</v>
+        <v>-14.37550695983692</v>
       </c>
       <c r="F20">
-        <v>-3.493623929573769</v>
+        <v>-3.664022417799239</v>
       </c>
       <c r="G20">
-        <v>-2.89178916358603</v>
+        <v>-2.957870963095422</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.558013829836661</v>
       </c>
       <c r="E21">
-        <v>-17.76111186829548</v>
+        <v>-15.88099361521292</v>
       </c>
       <c r="F21">
-        <v>-3.070705922278899</v>
+        <v>-3.510715634195732</v>
       </c>
       <c r="G21">
-        <v>-3.142192207085424</v>
+        <v>-1.923984280635491</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.707241624377182</v>
       </c>
       <c r="E22">
-        <v>-18.7285297705541</v>
+        <v>-15.45661220205811</v>
       </c>
       <c r="F22">
-        <v>-2.910900596400429</v>
+        <v>-3.016229996768595</v>
       </c>
       <c r="G22">
-        <v>-3.075593962471906</v>
+        <v>-2.407575530830069</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.236959702787213</v>
       </c>
       <c r="E23">
-        <v>-18.70451980136543</v>
+        <v>-16.0123420038054</v>
       </c>
       <c r="F23">
-        <v>-2.749451789594806</v>
+        <v>-2.950832047052379</v>
       </c>
       <c r="G23">
-        <v>-3.176939693065614</v>
+        <v>-2.301032243739705</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.111518949913144</v>
       </c>
       <c r="E24">
-        <v>-19.42231463089924</v>
+        <v>-17.07896518615006</v>
       </c>
       <c r="F24">
-        <v>-2.52939681740852</v>
+        <v>-2.585423446696864</v>
       </c>
       <c r="G24">
-        <v>-3.385742421318527</v>
+        <v>-1.653929838814983</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.281327052038345</v>
       </c>
       <c r="E25">
-        <v>-19.10718718165347</v>
+        <v>-17.38206953690545</v>
       </c>
       <c r="F25">
-        <v>-2.5861441263373</v>
+        <v>-2.393653079479168</v>
       </c>
       <c r="G25">
-        <v>-3.382368975414009</v>
+        <v>-2.128062860403864</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.684477717690816</v>
       </c>
       <c r="E26">
-        <v>-20.85842506447773</v>
+        <v>-17.58080161873207</v>
       </c>
       <c r="F26">
-        <v>-2.044742244317808</v>
+        <v>-2.358304157299504</v>
       </c>
       <c r="G26">
-        <v>-3.600620000636002</v>
+        <v>-2.281751626518989</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.255475922103369</v>
       </c>
       <c r="E27">
-        <v>-19.01000612944886</v>
+        <v>-18.06833260192385</v>
       </c>
       <c r="F27">
-        <v>-2.38693999004688</v>
+        <v>-2.642186494606298</v>
       </c>
       <c r="G27">
-        <v>-4.257915575276138</v>
+        <v>-2.196283272331625</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.933922951162002</v>
       </c>
       <c r="E28">
-        <v>-20.48225831408257</v>
+        <v>-17.9498722503572</v>
       </c>
       <c r="F28">
-        <v>-2.512049975626495</v>
+        <v>-2.602535032136494</v>
       </c>
       <c r="G28">
-        <v>-4.675425025961324</v>
+        <v>-2.760701491867509</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.665878590364393</v>
       </c>
       <c r="E29">
-        <v>-20.18929774510435</v>
+        <v>-17.62388099196704</v>
       </c>
       <c r="F29">
-        <v>-2.395825887176711</v>
+        <v>-2.571365223503954</v>
       </c>
       <c r="G29">
-        <v>-3.529761083913441</v>
+        <v>-2.404685424574285</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.408291362863624</v>
       </c>
       <c r="E30">
-        <v>-20.70882239716033</v>
+        <v>-17.28678138683606</v>
       </c>
       <c r="F30">
-        <v>-2.324482744610603</v>
+        <v>-2.645160333582348</v>
       </c>
       <c r="G30">
-        <v>-3.934395822996401</v>
+        <v>-2.536332578488943</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.132004470843048</v>
       </c>
       <c r="E31">
-        <v>-19.8325536197281</v>
+        <v>-17.52741543865564</v>
       </c>
       <c r="F31">
-        <v>-2.407905140644333</v>
+        <v>-2.627835029352796</v>
       </c>
       <c r="G31">
-        <v>-4.286760358559809</v>
+        <v>-2.312718469493332</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.813977323828565</v>
       </c>
       <c r="E32">
-        <v>-19.84256607575906</v>
+        <v>-17.36896413312726</v>
       </c>
       <c r="F32">
-        <v>-2.798566521274191</v>
+        <v>-2.831284548582563</v>
       </c>
       <c r="G32">
-        <v>-3.754427946390541</v>
+        <v>-2.102528622659465</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.440868876092773</v>
       </c>
       <c r="E33">
-        <v>-19.24000732429844</v>
+        <v>-16.89283584748679</v>
       </c>
       <c r="F33">
-        <v>-2.762073623711262</v>
+        <v>-3.03292905524163</v>
       </c>
       <c r="G33">
-        <v>-2.476805659147308</v>
+        <v>-2.114075805500442</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.00321056895444</v>
       </c>
       <c r="E34">
-        <v>-19.00624296754849</v>
+        <v>-16.65807975492916</v>
       </c>
       <c r="F34">
-        <v>-2.956252883336299</v>
+        <v>-3.126688648094895</v>
       </c>
       <c r="G34">
-        <v>-3.185709328199144</v>
+        <v>-1.595061718035663</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.49406894803216</v>
       </c>
       <c r="E35">
-        <v>-18.78660744970247</v>
+        <v>-16.25022727190234</v>
       </c>
       <c r="F35">
-        <v>-2.919188412265438</v>
+        <v>-2.803376022414845</v>
       </c>
       <c r="G35">
-        <v>-3.213130576900927</v>
+        <v>-2.239151526519648</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.9084544708808</v>
       </c>
       <c r="E36">
-        <v>-18.59364464376163</v>
+        <v>-15.93561606869344</v>
       </c>
       <c r="F36">
-        <v>-2.647505441699673</v>
+        <v>-3.397258292871297</v>
       </c>
       <c r="G36">
-        <v>-2.348988806421587</v>
+        <v>-1.935180545649306</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.24105875475316</v>
       </c>
       <c r="E37">
-        <v>-18.67033435108153</v>
+        <v>-15.76294535478097</v>
       </c>
       <c r="F37">
-        <v>-2.964704715947063</v>
+        <v>-3.145182778729797</v>
       </c>
       <c r="G37">
-        <v>-2.991201535584804</v>
+        <v>-1.583981322115722</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.48350485624439</v>
       </c>
       <c r="E38">
-        <v>-18.61748705941201</v>
+        <v>-15.19556378941194</v>
       </c>
       <c r="F38">
-        <v>-2.864379483059209</v>
+        <v>-3.296500652199182</v>
       </c>
       <c r="G38">
-        <v>-2.302194245223989</v>
+        <v>-1.605844164857069</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.62816653099761</v>
       </c>
       <c r="E39">
-        <v>-18.13555327009371</v>
+        <v>-15.03716682557165</v>
       </c>
       <c r="F39">
-        <v>-2.766744787495648</v>
+        <v>-3.017083215193478</v>
       </c>
       <c r="G39">
-        <v>-3.207929709858732</v>
+        <v>-1.381164060197812</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.66518198257788</v>
       </c>
       <c r="E40">
-        <v>-17.7060410958882</v>
+        <v>-14.69617726126807</v>
       </c>
       <c r="F40">
-        <v>-2.63522158148356</v>
+        <v>-3.20594932629696</v>
       </c>
       <c r="G40">
-        <v>-1.560284437145619</v>
+        <v>-1.094467505951388</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.5850774838357</v>
       </c>
       <c r="E41">
-        <v>-17.94122286500255</v>
+        <v>-14.81383154446136</v>
       </c>
       <c r="F41">
-        <v>-2.944157890888024</v>
+        <v>-3.036643454675783</v>
       </c>
       <c r="G41">
-        <v>-1.412296430449119</v>
+        <v>-0.9746423101574677</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.38494422426646</v>
       </c>
       <c r="E42">
-        <v>-16.68027833451476</v>
+        <v>-13.26607158422375</v>
       </c>
       <c r="F42">
-        <v>-2.768249102699132</v>
+        <v>-3.272173158313767</v>
       </c>
       <c r="G42">
-        <v>-1.624598405337041</v>
+        <v>-1.352309345277525</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.0674007040099</v>
       </c>
       <c r="E43">
-        <v>-16.5809417286825</v>
+        <v>-13.87107118317451</v>
       </c>
       <c r="F43">
-        <v>-2.499530859067987</v>
+        <v>-3.391898755775185</v>
       </c>
       <c r="G43">
-        <v>-2.035844303861925</v>
+        <v>-1.261815582961547</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.64464801841673</v>
       </c>
       <c r="E44">
-        <v>-16.52653211348034</v>
+        <v>-12.75790887345302</v>
       </c>
       <c r="F44">
-        <v>-2.999578983604922</v>
+        <v>-3.42569780254421</v>
       </c>
       <c r="G44">
-        <v>-1.388741898937204</v>
+        <v>-0.5813495000920507</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.13777806933428</v>
       </c>
       <c r="E45">
-        <v>-15.81848708848505</v>
+        <v>-12.45043907375423</v>
       </c>
       <c r="F45">
-        <v>-2.613716335339481</v>
+        <v>-3.274566311740454</v>
       </c>
       <c r="G45">
-        <v>-2.250198816984196</v>
+        <v>-0.8714393635162277</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.574133354102258</v>
       </c>
       <c r="E46">
-        <v>-15.23400147678904</v>
+        <v>-12.87523257804375</v>
       </c>
       <c r="F46">
-        <v>-3.097293202439152</v>
+        <v>-3.781025999975058</v>
       </c>
       <c r="G46">
-        <v>-1.714171835993101</v>
+        <v>-0.3384514633301844</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.986191494604775</v>
       </c>
       <c r="E47">
-        <v>-16.09660784814013</v>
+        <v>-12.01146238887269</v>
       </c>
       <c r="F47">
-        <v>-3.152663764744479</v>
+        <v>-3.594321927792883</v>
       </c>
       <c r="G47">
-        <v>-1.35523586753424</v>
+        <v>-0.7557093125543856</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.410859949136286</v>
       </c>
       <c r="E48">
-        <v>-14.82392098455045</v>
+        <v>-12.19135601882739</v>
       </c>
       <c r="F48">
-        <v>-2.991161942425076</v>
+        <v>-3.627672827796994</v>
       </c>
       <c r="G48">
-        <v>-1.961797331785047</v>
+        <v>-0.8293126715290019</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.881472783580095</v>
       </c>
       <c r="E49">
-        <v>-13.84279991994462</v>
+        <v>-11.28908474364312</v>
       </c>
       <c r="F49">
-        <v>-3.178015120739755</v>
+        <v>-3.867955703592241</v>
       </c>
       <c r="G49">
-        <v>-2.065324711889135</v>
+        <v>-0.4686585299352595</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.431364051635109</v>
       </c>
       <c r="E50">
-        <v>-12.42331351444828</v>
+        <v>-11.36778056494842</v>
       </c>
       <c r="F50">
-        <v>-3.343388732299843</v>
+        <v>-3.821200990643431</v>
       </c>
       <c r="G50">
-        <v>-1.464222337232587</v>
+        <v>-1.3367961288805</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.088171286565854</v>
       </c>
       <c r="E51">
-        <v>-13.73353689908755</v>
+        <v>-10.14475747580085</v>
       </c>
       <c r="F51">
-        <v>-3.1401239390009</v>
+        <v>-4.106335819463258</v>
       </c>
       <c r="G51">
-        <v>-1.917349947374792</v>
+        <v>-0.5106859055563072</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.870995581175386</v>
       </c>
       <c r="E52">
-        <v>-13.77109153403316</v>
+        <v>-10.60482779261012</v>
       </c>
       <c r="F52">
-        <v>-3.235193180717991</v>
+        <v>-4.015284988017147</v>
       </c>
       <c r="G52">
-        <v>-1.724686128625826</v>
+        <v>-0.5012674034970807</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.793143134634566</v>
       </c>
       <c r="E53">
-        <v>-13.65823743328801</v>
+        <v>-10.47387338125631</v>
       </c>
       <c r="F53">
-        <v>-3.7794405047661</v>
+        <v>-4.016066138477987</v>
       </c>
       <c r="G53">
-        <v>-1.857038428740349</v>
+        <v>-0.3742185973364703</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.857309421871824</v>
       </c>
       <c r="E54">
-        <v>-12.31809894935407</v>
+        <v>-9.661972333369107</v>
       </c>
       <c r="F54">
-        <v>-3.345363560188117</v>
+        <v>-3.841342744042501</v>
       </c>
       <c r="G54">
-        <v>-2.491408475521034</v>
+        <v>-0.6252771288526401</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.053672608900537</v>
       </c>
       <c r="E55">
-        <v>-13.32613726346149</v>
+        <v>-8.543045276235862</v>
       </c>
       <c r="F55">
-        <v>-3.426308309320073</v>
+        <v>-4.011727978389525</v>
       </c>
       <c r="G55">
-        <v>-2.531598498367785</v>
+        <v>-1.384792418108854</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.363043861085696</v>
       </c>
       <c r="E56">
-        <v>-11.72077511384632</v>
+        <v>-9.32068388978103</v>
       </c>
       <c r="F56">
-        <v>-3.462266909908197</v>
+        <v>-4.190663621068247</v>
       </c>
       <c r="G56">
-        <v>-2.239310432705532</v>
+        <v>-0.713585931112699</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.755684223802723</v>
       </c>
       <c r="E57">
-        <v>-13.93640347768317</v>
+        <v>-8.434321143785704</v>
       </c>
       <c r="F57">
-        <v>-3.806954728050085</v>
+        <v>-4.294910345240954</v>
       </c>
       <c r="G57">
-        <v>-2.558261632141076</v>
+        <v>-0.6790801149568755</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.196750798843087</v>
       </c>
       <c r="E58">
-        <v>-12.50389318094077</v>
+        <v>-9.333689667131059</v>
       </c>
       <c r="F58">
-        <v>-3.463366981819115</v>
+        <v>-4.351303941288738</v>
       </c>
       <c r="G58">
-        <v>-1.948455833261784</v>
+        <v>-1.031106974875277</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.655594184573676</v>
       </c>
       <c r="E59">
-        <v>-11.2778541281041</v>
+        <v>-9.3571516909648</v>
       </c>
       <c r="F59">
-        <v>-3.728302071521675</v>
+        <v>-4.131950596292624</v>
       </c>
       <c r="G59">
-        <v>-3.159453391527184</v>
+        <v>-0.8104756674105489</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.100844676590146</v>
       </c>
       <c r="E60">
-        <v>-11.19501475308178</v>
+        <v>-8.853358957611473</v>
       </c>
       <c r="F60">
-        <v>-3.628912065431582</v>
+        <v>-4.448913785830215</v>
       </c>
       <c r="G60">
-        <v>-1.829560900764398</v>
+        <v>-1.193836840858152</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.505308110060783</v>
       </c>
       <c r="E61">
-        <v>-10.9756962284163</v>
+        <v>-7.58146457697313</v>
       </c>
       <c r="F61">
-        <v>-3.890007672222167</v>
+        <v>-4.593273373116086</v>
       </c>
       <c r="G61">
-        <v>-2.627640735007582</v>
+        <v>-1.179300235395212</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.847831260062652</v>
       </c>
       <c r="E62">
-        <v>-10.80547089046797</v>
+        <v>-8.712102267890211</v>
       </c>
       <c r="F62">
-        <v>-3.634959147472018</v>
+        <v>-4.117265298975794</v>
       </c>
       <c r="G62">
-        <v>-2.265685549016906</v>
+        <v>-1.315270961784159</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.11405294626204</v>
       </c>
       <c r="E63">
-        <v>-10.76337872456668</v>
+        <v>-7.530822652145353</v>
       </c>
       <c r="F63">
-        <v>-3.945870284764757</v>
+        <v>-4.163602514753593</v>
       </c>
       <c r="G63">
-        <v>-3.19126773415958</v>
+        <v>-1.126732082777125</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.29569068115004</v>
       </c>
       <c r="E64">
-        <v>-10.76554786361635</v>
+        <v>-7.125266105440419</v>
       </c>
       <c r="F64">
-        <v>-3.804993982407659</v>
+        <v>-4.353501600008365</v>
       </c>
       <c r="G64">
-        <v>-2.69705625387502</v>
+        <v>-1.612183859564774</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.38976608709667</v>
       </c>
       <c r="E65">
-        <v>-10.39128760077843</v>
+        <v>-8.252185919197203</v>
       </c>
       <c r="F65">
-        <v>-3.539615716144601</v>
+        <v>-4.568468739606657</v>
       </c>
       <c r="G65">
-        <v>-2.796111086955553</v>
+        <v>-1.564346476522305</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.39544768309462</v>
       </c>
       <c r="E66">
-        <v>-11.07333918496969</v>
+        <v>-7.704181694106989</v>
       </c>
       <c r="F66">
-        <v>-3.859850128555848</v>
+        <v>-4.176086011513782</v>
       </c>
       <c r="G66">
-        <v>-2.832196033333609</v>
+        <v>-1.85862418005366</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.31971040819959</v>
       </c>
       <c r="E67">
-        <v>-10.19941162859942</v>
+        <v>-7.43985466627927</v>
       </c>
       <c r="F67">
-        <v>-3.636338379197679</v>
+        <v>-4.470788483835942</v>
       </c>
       <c r="G67">
-        <v>-2.884678111767676</v>
+        <v>-1.455508981373225</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.17295262163183</v>
       </c>
       <c r="E68">
-        <v>-10.75592032787604</v>
+        <v>-7.388918390640995</v>
       </c>
       <c r="F68">
-        <v>-3.754717051262145</v>
+        <v>-4.580067539980655</v>
       </c>
       <c r="G68">
-        <v>-3.069462832133175</v>
+        <v>-1.397034815513079</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.967572783514848</v>
       </c>
       <c r="E69">
-        <v>-11.06358032348316</v>
+        <v>-7.116095945574886</v>
       </c>
       <c r="F69">
-        <v>-4.115965590520801</v>
+        <v>-4.56307275434482</v>
       </c>
       <c r="G69">
-        <v>-2.636023036313017</v>
+        <v>-0.9744304352429544</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.719317268509283</v>
       </c>
       <c r="E70">
-        <v>-10.62517875480059</v>
+        <v>-6.905395106946</v>
       </c>
       <c r="F70">
-        <v>-3.770973761542086</v>
+        <v>-4.556038258360247</v>
       </c>
       <c r="G70">
-        <v>-2.489941903847136</v>
+        <v>-1.32543764713526</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.441722394502595</v>
       </c>
       <c r="E71">
-        <v>-10.69889778317146</v>
+        <v>-8.0096544367684</v>
       </c>
       <c r="F71">
-        <v>-3.676872052951465</v>
+        <v>-4.636161267028627</v>
       </c>
       <c r="G71">
-        <v>-2.645080688908462</v>
+        <v>-1.267698422384832</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.147808500037232</v>
       </c>
       <c r="E72">
-        <v>-10.16299364062974</v>
+        <v>-7.126891827609172</v>
       </c>
       <c r="F72">
-        <v>-3.475886098377624</v>
+        <v>-4.73738610691592</v>
       </c>
       <c r="G72">
-        <v>-3.199494439824669</v>
+        <v>-1.08814767451692</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.850308323694616</v>
       </c>
       <c r="E73">
-        <v>-10.97583661111054</v>
+        <v>-7.669941902134994</v>
       </c>
       <c r="F73">
-        <v>-3.943405891741428</v>
+        <v>-4.766484997041462</v>
       </c>
       <c r="G73">
-        <v>-3.078401305089208</v>
+        <v>-0.8513675259116266</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.559346284213182</v>
       </c>
       <c r="E74">
-        <v>-11.9787622780633</v>
+        <v>-7.898317374815818</v>
       </c>
       <c r="F74">
-        <v>-4.249533207282999</v>
+        <v>-4.787933914202149</v>
       </c>
       <c r="G74">
-        <v>-2.744287807083802</v>
+        <v>-0.9345184982215009</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.283159629546777</v>
       </c>
       <c r="E75">
-        <v>-10.49495795623602</v>
+        <v>-8.158532548244571</v>
       </c>
       <c r="F75">
-        <v>-3.763970743518819</v>
+        <v>-4.878935871971494</v>
       </c>
       <c r="G75">
-        <v>-2.325341579634573</v>
+        <v>-0.5337637185105667</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.031276996896407</v>
       </c>
       <c r="E76">
-        <v>-11.69013998718443</v>
+        <v>-8.890229792981925</v>
       </c>
       <c r="F76">
-        <v>-4.132132837121239</v>
+        <v>-4.919224348974051</v>
       </c>
       <c r="G76">
-        <v>-2.411359484381456</v>
+        <v>-0.5867390682299842</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.80997309757168</v>
       </c>
       <c r="E77">
-        <v>-11.28672088021112</v>
+        <v>-9.119868709910889</v>
       </c>
       <c r="F77">
-        <v>-4.195045684629056</v>
+        <v>-4.991744601619537</v>
       </c>
       <c r="G77">
-        <v>-1.919995073260669</v>
+        <v>-0.372248822740604</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.627457365514132</v>
       </c>
       <c r="E78">
-        <v>-11.41177921840694</v>
+        <v>-8.778213459928191</v>
       </c>
       <c r="F78">
-        <v>-4.380418570394933</v>
+        <v>-5.013548060028623</v>
       </c>
       <c r="G78">
-        <v>-2.848814971940751</v>
+        <v>-0.4107802622721813</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.489821413175054</v>
       </c>
       <c r="E79">
-        <v>-12.58970776338612</v>
+        <v>-10.21719494602755</v>
       </c>
       <c r="F79">
-        <v>-4.832583745580446</v>
+        <v>-5.280197041887575</v>
       </c>
       <c r="G79">
-        <v>-1.705875608871688</v>
+        <v>-0.4209833636242151</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.397676117809072</v>
       </c>
       <c r="E80">
-        <v>-13.2807438400086</v>
+        <v>-11.16795712088595</v>
       </c>
       <c r="F80">
-        <v>-4.587814431931636</v>
+        <v>-5.350704361744258</v>
       </c>
       <c r="G80">
-        <v>-2.129665164444871</v>
+        <v>-0.07717658827982382</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.348884402527868</v>
       </c>
       <c r="E81">
-        <v>-14.00194861047019</v>
+        <v>-11.4902757868559</v>
       </c>
       <c r="F81">
-        <v>-4.070327516830965</v>
+        <v>-5.035536244368533</v>
       </c>
       <c r="G81">
-        <v>-2.226859470932334</v>
+        <v>-0.0990328099300922</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.337587028700279</v>
       </c>
       <c r="E82">
-        <v>-14.9235474127192</v>
+        <v>-11.80764483073546</v>
       </c>
       <c r="F82">
-        <v>-4.294085291307765</v>
+        <v>-5.577629813169363</v>
       </c>
       <c r="G82">
-        <v>-2.107166696959984</v>
+        <v>-0.09236206066846075</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.35396134215799</v>
       </c>
       <c r="E83">
-        <v>-14.81760376330975</v>
+        <v>-13.13800633928684</v>
       </c>
       <c r="F83">
-        <v>-4.719726970623041</v>
+        <v>-5.606397356333784</v>
       </c>
       <c r="G83">
-        <v>-2.185133354955359</v>
+        <v>0.4300486465196111</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.386951963690876</v>
       </c>
       <c r="E84">
-        <v>-15.30973567609332</v>
+        <v>-13.51162808728968</v>
       </c>
       <c r="F84">
-        <v>-4.993283708253938</v>
+        <v>-5.409457148155216</v>
       </c>
       <c r="G84">
-        <v>-2.440051982570319</v>
+        <v>0.5384491496575069</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.421679110863792</v>
       </c>
       <c r="E85">
-        <v>-18.19505289008049</v>
+        <v>-15.21173949856734</v>
       </c>
       <c r="F85">
-        <v>-4.610943278185202</v>
+        <v>-5.839245634688906</v>
       </c>
       <c r="G85">
-        <v>-2.047272307063489</v>
+        <v>0.4521995067228746</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.439661282952732</v>
       </c>
       <c r="E86">
-        <v>-17.57870040679251</v>
+        <v>-15.72744211856084</v>
       </c>
       <c r="F86">
-        <v>-4.776455227101557</v>
+        <v>-5.593525355261683</v>
       </c>
       <c r="G86">
-        <v>-2.031411483384841</v>
+        <v>0.1827873107369854</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.425399366481609</v>
       </c>
       <c r="E87">
-        <v>-18.88651011478569</v>
+        <v>-17.27402920403046</v>
       </c>
       <c r="F87">
-        <v>-4.970945952870047</v>
+        <v>-5.608983519365324</v>
       </c>
       <c r="G87">
-        <v>-2.250049842434928</v>
+        <v>0.2886420043551816</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.363324082791211</v>
       </c>
       <c r="E88">
-        <v>-20.62535809272496</v>
+        <v>-17.87267988242245</v>
       </c>
       <c r="F88">
-        <v>-4.532930949659155</v>
+        <v>-5.957905123302921</v>
       </c>
       <c r="G88">
-        <v>-1.074888939632139</v>
+        <v>0.8140520658018332</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.243144457079847</v>
       </c>
       <c r="E89">
-        <v>-23.55692008327846</v>
+        <v>-20.11403903557088</v>
       </c>
       <c r="F89">
-        <v>-5.335419326427801</v>
+        <v>-5.67049062739059</v>
       </c>
       <c r="G89">
-        <v>-1.954901465426745</v>
+        <v>0.5243396045691331</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.061374765419607</v>
       </c>
       <c r="E90">
-        <v>-23.45523319943622</v>
+        <v>-21.11842739962812</v>
       </c>
       <c r="F90">
-        <v>-5.316218598398311</v>
+        <v>-5.817508445672043</v>
       </c>
       <c r="G90">
-        <v>-1.526629431193388</v>
+        <v>0.2376695346870231</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.823465969681854</v>
       </c>
       <c r="E91">
-        <v>-25.55034981298094</v>
+        <v>-23.02201673349243</v>
       </c>
       <c r="F91">
-        <v>-4.901932179440612</v>
+        <v>-5.604771271122089</v>
       </c>
       <c r="G91">
-        <v>-2.056462381480506</v>
+        <v>-0.4017722678598245</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.546879059935486</v>
       </c>
       <c r="E92">
-        <v>-27.38865666555068</v>
+        <v>-26.20225081722914</v>
       </c>
       <c r="F92">
-        <v>-5.333006292183446</v>
+        <v>-5.997032229206752</v>
       </c>
       <c r="G92">
-        <v>-2.484393429523318</v>
+        <v>-0.02990530852457055</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.260454175564516</v>
       </c>
       <c r="E93">
-        <v>-29.18967153466724</v>
+        <v>-27.73821410267676</v>
       </c>
       <c r="F93">
-        <v>-5.161949251872751</v>
+        <v>-6.056253871567695</v>
       </c>
       <c r="G93">
-        <v>-2.201494071010438</v>
+        <v>0.01590602064786414</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.997559878216963</v>
       </c>
       <c r="E94">
-        <v>-30.9360639503033</v>
+        <v>-29.51090110263835</v>
       </c>
       <c r="F94">
-        <v>-4.880180908177902</v>
+        <v>-5.711778943848326</v>
       </c>
       <c r="G94">
-        <v>-2.462543828964128</v>
+        <v>-0.525894551763719</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.793696523604106</v>
       </c>
       <c r="E95">
-        <v>-32.9716628299652</v>
+        <v>-32.4947465898474</v>
       </c>
       <c r="F95">
-        <v>-4.598197188958325</v>
+        <v>-5.864775089675784</v>
       </c>
       <c r="G95">
-        <v>-3.787924046156887</v>
+        <v>-0.3687727499243693</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.684053497636641</v>
       </c>
       <c r="E96">
-        <v>-36.19046366258823</v>
+        <v>-33.52607484577627</v>
       </c>
       <c r="F96">
-        <v>-5.367312299802985</v>
+        <v>-5.926245749535326</v>
       </c>
       <c r="G96">
-        <v>-3.145218045708318</v>
+        <v>-0.8046524178069708</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.680154999097381</v>
       </c>
       <c r="E97">
-        <v>-37.37721820340836</v>
+        <v>-34.95301511948923</v>
       </c>
       <c r="F97">
-        <v>-4.986595469843735</v>
+        <v>-5.855497374764429</v>
       </c>
       <c r="G97">
-        <v>-3.170490750355114</v>
+        <v>-1.715198105110275</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.800622329132279</v>
       </c>
       <c r="E98">
-        <v>-40.8187792009427</v>
+        <v>-38.43423196390874</v>
       </c>
       <c r="F98">
-        <v>-4.847376730659639</v>
+        <v>-5.959080576647493</v>
       </c>
       <c r="G98">
-        <v>-3.857829525764137</v>
+        <v>-1.5858087432534</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.018799826959319</v>
       </c>
       <c r="E99">
-        <v>-43.69667877450531</v>
+        <v>-41.47945185934375</v>
       </c>
       <c r="F99">
-        <v>-5.477012994955723</v>
+        <v>-5.842480409396837</v>
       </c>
       <c r="G99">
-        <v>-3.826561423145721</v>
+        <v>-2.238774124328171</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.347071393418299</v>
       </c>
       <c r="E100">
-        <v>-45.2299091258893</v>
+        <v>-43.64744294085691</v>
       </c>
       <c r="F100">
-        <v>-4.928683476346619</v>
+        <v>-5.821117642446041</v>
       </c>
       <c r="G100">
-        <v>-4.414007797452776</v>
+        <v>-2.711284978602808</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.71457821532586</v>
       </c>
       <c r="E101">
-        <v>-47.67560887592284</v>
+        <v>-45.82381169928426</v>
       </c>
       <c r="F101">
-        <v>-4.442001888221256</v>
+        <v>-5.58202595897602</v>
       </c>
       <c r="G101">
-        <v>-4.414335541461163</v>
+        <v>-3.094596493867322</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.177055129844439</v>
       </c>
       <c r="E102">
-        <v>-49.78683213939434</v>
+        <v>-48.52226596181892</v>
       </c>
       <c r="F102">
-        <v>-4.803503907905169</v>
+        <v>-5.390231569103642</v>
       </c>
       <c r="G102">
-        <v>-4.84701060126175</v>
+        <v>-3.566412133578713</v>
       </c>
     </row>
   </sheetData>
